--- a/public/data/monthly-revenue-11507.xlsx
+++ b/public/data/monthly-revenue-11507.xlsx
@@ -832,34 +832,34 @@
         <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v>27</v>
+        <v>上市公司</v>
       </c>
       <c r="D11" t="str">
         <v>11507</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>139,577</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>152,849</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>-13,272</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>-8.68</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>984,463</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>894,886</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>89,577</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>10.01</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -1406,34 +1406,34 @@
         <v>佐茂</v>
       </c>
       <c r="C25" t="str">
-        <v>25</v>
+        <v>興櫃公司</v>
       </c>
       <c r="D25" t="str">
         <v>11507</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>178,653</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>139,246</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>39,407</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>28.30</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>1,070,386</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>968,388</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>101,998</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>10.53</v>
       </c>
       <c r="M25" t="str">
         <v/>
